--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA204"/>
+  <dimension ref="A1:AA205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22412,6 +22412,91 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Sir I Fino Doo</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Sir I Fino Doo</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>110237</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Novi Sad</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Vojvodina, Južnobački okrug</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>29 Fruškogorska</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>https://sirifino.rs</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>info@sirifino.rs</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr"/>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>21422355</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr"/>
+      <c r="S205" s="2" t="inlineStr"/>
+      <c r="T205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sirifinons</t>
+        </is>
+      </c>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr"/>
+      <c r="X205" s="2" t="inlineStr"/>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA205"/>
+  <dimension ref="A1:AA208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22497,6 +22497,317 @@
       <c r="Z205" s="2" t="inlineStr"/>
       <c r="AA205" s="2" t="inlineStr"/>
     </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>122538</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>86a Bulevar Milutina Milankovića</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>11070</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.supervero.rs</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>info@veropoulos.rs</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 112111</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>17330012</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veropoulos-srbija/</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Super.Vero.Srbija</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/superveroserbia</t>
+        </is>
+      </c>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCEpFGezJmL7tg6aAQeLXV5Q</t>
+        </is>
+      </c>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>Jelena Gvozdenović</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jelena-gvozdenovi%C4%87-636301204/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>122538</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>86a Bulevar Milutina Milankovića</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>11070</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.supervero.rs</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>info@veropoulos.rs</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 112111</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>17330012</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veropoulos-srbija/</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Super.Vero.Srbija</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/superveroserbia</t>
+        </is>
+      </c>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCEpFGezJmL7tg6aAQeLXV5Q</t>
+        </is>
+      </c>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>Marc Ernest</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marc-ernest-garofani-32449229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Sir I Fino Doo</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Sir I Fino Doo</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>110237</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Novi Sad</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Vojvodina, Južnobački okrug</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>29 Fruškogorska</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>https://sirifino.rs</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>info@sirifino.rs</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr"/>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>21422355</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr"/>
+      <c r="S208" s="2" t="inlineStr"/>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sirifinons</t>
+        </is>
+      </c>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
+      <c r="X208" s="2" t="inlineStr"/>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA208"/>
+  <dimension ref="A1:AA211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22808,6 +22808,317 @@
       <c r="Z208" s="2" t="inlineStr"/>
       <c r="AA208" s="2" t="inlineStr"/>
     </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>122538</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>86a Bulevar Milutina Milankovića</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>11070</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.supervero.rs</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>info@veropoulos.rs</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 112111</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>17330012</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veropoulos-srbija/</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Super.Vero.Srbija</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/superveroserbia</t>
+        </is>
+      </c>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCEpFGezJmL7tg6aAQeLXV5Q</t>
+        </is>
+      </c>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>Jelena Gvozdenović</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jelena-gvozdenovi%C4%87-636301204/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Veropoulos D.o.o</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>122538</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>86a Bulevar Milutina Milankovića</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>11070</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.supervero.rs</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>info@veropoulos.rs</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 112111</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>17330012</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veropoulos-srbija/</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Super.Vero.Srbija</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/superveroserbia</t>
+        </is>
+      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCEpFGezJmL7tg6aAQeLXV5Q</t>
+        </is>
+      </c>
+      <c r="W210" s="2" t="inlineStr">
+        <is>
+          <t>Marc Ernest</t>
+        </is>
+      </c>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marc-ernest-garofani-32449229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Sir I Fino Doo</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Sir I Fino Doo</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>110237</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Novi Sad</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Vojvodina, Južnobački okrug</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>29 Fruškogorska</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://sirifino.rs</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>info@sirifino.rs</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr"/>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>21422355</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr"/>
+      <c r="S211" s="2" t="inlineStr"/>
+      <c r="T211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sirifinons</t>
+        </is>
+      </c>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr"/>
+      <c r="X211" s="2" t="inlineStr"/>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
